--- a/NRCS/Requirements/NRCS_information.xlsx
+++ b/NRCS/Requirements/NRCS_information.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Period Plan" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,175 +14,31 @@
     <sheet name="Activity Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri (Body)"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF7030A0"/>
-      <sz val="11"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F497D"/>
-        <bgColor rgb="FF1F497D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9EDF4"/>
-        <bgColor rgb="FFE9EDF4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.5999938962981048"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002A4D69"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -189,247 +46,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="PivotTable Style 1" table="0" count="0"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -512,44 +139,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -576,32 +203,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -628,24 +237,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -657,162 +248,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -822,804 +417,773 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="14.25"/>
-  <cols>
-    <col width="11.3125" bestFit="1" customWidth="1" style="13" min="1" max="1"/>
-    <col width="10" customWidth="1" style="13" min="2" max="16384"/>
-  </cols>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Weekly Period Plan</t>
         </is>
       </c>
-      <c r="B1" s="36" t="n"/>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="36" t="n"/>
-      <c r="E1" s="36" t="n"/>
-      <c r="F1" s="36" t="n"/>
-      <c r="G1" s="36" t="n"/>
-      <c r="H1" s="36" t="n"/>
-      <c r="I1" s="36" t="n"/>
-      <c r="J1" s="36" t="n"/>
-      <c r="K1" s="36" t="n"/>
-      <c r="L1" s="36" t="n"/>
-      <c r="M1" s="37" t="n"/>
-      <c r="N1" s="17" t="n"/>
-      <c r="O1" s="16" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>Subjects</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>L.K.G</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>U.K.G</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Class 1</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Class 2</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Class 3</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Class 4</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Class 5</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Class 6</t>
         </is>
       </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Class 7 </t>
-        </is>
-      </c>
-      <c r="K2" s="18" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Class 8</t>
         </is>
       </c>
-      <c r="L2" s="18" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Class 9</t>
         </is>
       </c>
-      <c r="M2" s="18" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Class 10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Telugu</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" s="20" t="n">
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Hindi</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="20" t="n">
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="20" t="n">
+      <c r="H4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="20" t="n">
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="20" t="n">
+      <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" s="20" t="n">
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="20" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="20" t="n">
+      <c r="M4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" s="20" t="n">
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Eng Grammar</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="20" t="n">
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Maths</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" t="n">
         <v>7</v>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" t="n">
         <v>7</v>
       </c>
-      <c r="L7" s="20" t="n">
+      <c r="L7" t="n">
         <v>7</v>
       </c>
-      <c r="M7" s="20" t="n">
+      <c r="M7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>EVS</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="20" t="n">
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="20" t="n">
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="20" t="n">
+      <c r="M9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Chemisty</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="20" t="n">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="20" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="20" t="n">
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="20" t="n">
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="20" t="n">
+      <c r="M10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="20" t="n">
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" s="20" t="n">
+      <c r="M11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Social</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" s="20" t="n">
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Oral</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20" t="n">
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>G.K</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="20" t="n">
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="20" t="n">
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Computer</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="20" t="n">
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="20" t="n">
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>P.E.T</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="20" t="n">
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Karate</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" s="14">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B18" s="22">
-        <f>SUM(B3:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="22">
-        <f>SUM(C3:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="22">
-        <f>SUM(D3:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="22">
-        <f>SUM(E3:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="22">
-        <f>SUM(F3:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="22">
-        <f>SUM(G3:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="22">
-        <f>SUM(H3:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="22">
-        <f>SUM(I3:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="22">
-        <f>SUM(J3:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="22">
-        <f>SUM(K3:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="22" t="n">
+      <c r="B18" t="n">
+        <v>42</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42</v>
+      </c>
+      <c r="D18" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" t="n">
+        <v>42</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42</v>
+      </c>
+      <c r="G18" t="n">
+        <v>42</v>
+      </c>
+      <c r="H18" t="n">
+        <v>42</v>
+      </c>
+      <c r="I18" t="n">
+        <v>42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>42</v>
+      </c>
+      <c r="K18" t="n">
+        <v>42</v>
+      </c>
+      <c r="L18" t="n">
         <v>40</v>
       </c>
-      <c r="M18" s="22" t="n">
+      <c r="M18" t="n">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1629,847 +1193,807 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="9.0625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="9.8125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.0625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="12.1875" bestFit="1" customWidth="1" min="4" max="11"/>
-    <col width="11.1875" bestFit="1" customWidth="1" min="12" max="13"/>
-  </cols>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Teacher Allotment</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
-      <c r="E1" s="38" t="n"/>
-      <c r="F1" s="38" t="n"/>
-      <c r="G1" s="38" t="n"/>
-      <c r="H1" s="38" t="n"/>
-      <c r="I1" s="38" t="n"/>
-      <c r="J1" s="38" t="n"/>
-      <c r="K1" s="38" t="n"/>
-      <c r="L1" s="38" t="n"/>
-      <c r="M1" s="38" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Subjects</t>
-        </is>
-      </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>L.K.G</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>U.K.G</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Class 1</t>
         </is>
       </c>
-      <c r="E2" s="25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Class 2</t>
         </is>
       </c>
-      <c r="F2" s="25" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Class 3</t>
         </is>
       </c>
-      <c r="G2" s="25" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Class 4</t>
         </is>
       </c>
-      <c r="H2" s="25" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Class 5</t>
         </is>
       </c>
-      <c r="I2" s="25" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Class 6</t>
         </is>
       </c>
-      <c r="J2" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Class 7 </t>
-        </is>
-      </c>
-      <c r="K2" s="25" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Class 8</t>
         </is>
       </c>
-      <c r="L2" s="25" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Class 9</t>
         </is>
       </c>
-      <c r="M2" s="26" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Class 10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Telugu</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>NAGAMANI</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>NAGAMANI</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>NAGAMANI</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>NAGAMANI</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>SWATHI</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>SWATHI</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>SWATHI</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SWATHI</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>D.V.RAO</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>D.V.RAO</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>D.V.RAO</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>D.V.RAO</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Hindi</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>SWATHI</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>SAI LAKSHMI</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>SAI LAKSHMI</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>RIYA</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>RIYA</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>RIYA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>SITHA</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>SAI LAKSHMI</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>MAHA</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>MAHA</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>MAHA</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>MAHA</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>MAHA</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>SONU</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>SONU</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>SONU</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Eng Gram</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Maths</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>SITHA</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>BHAVANI</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>BHAVANI</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>TULASI</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>TULASI</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>TULASI</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>TULASI</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>GOWTHAM</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>GOWTHAM</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>EVS</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SITHA</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>BHAVANI</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>SAI LAKSHMI</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SAI LAKSHMI</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="9" t="n"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Phy/Che</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>BHEEMA</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>BHEEMA</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>BHEEMA</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Chemisty</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>BHEEMA</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>BHEEMA</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>BHEEMA</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>CHALAPATHI</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>CHALAPATHI</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>CHALAPATHI</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Social</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>PALLAVI</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>PALLAVI</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>PALLAVI</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>PALLAVI</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>PALLAVI</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>SUNITHA</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>SUNITHA</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>SUNITHA</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>G.K</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>NAGAMANI</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>BHAVANI</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>SAI LAKSHMI</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="L13" s="8" t="n"/>
-      <c r="M13" s="9" t="n"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Computer</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="9" t="n"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>P.E.T</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>P.E</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Karate</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="L16" s="10" t="n"/>
-      <c r="M16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="D21" s="35" t="n"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2479,212 +2003,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-  </cols>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Period 1 Teacher Allotment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>L.K.G</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>U.K.G</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Class 1</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Class 2</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Class 3</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Class 4</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Class 5</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Class 6</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Class 7</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Class 8</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Class 9</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Class 10</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Period 1 Teacher</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Sitha</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bhavani</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Naga mani</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Sai Lakshmi</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Swathi</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Tulasi</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Maha</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Sangeetha</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Pallavi</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Fathima</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>D.V.Rao</t>
         </is>
       </c>
-      <c r="N2" s="6" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Study Hour</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Sitha</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bhavani</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Naga mani</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Sai Lakshmi</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Swathi</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Tulasi</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Sangeetha</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Pallavi</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Fathima</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>D.V.Rao</t>
         </is>
       </c>
-      <c r="N3" s="6" t="n"/>
+      <c r="M4" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2695,680 +2214,662 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="12.75" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="15.1875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.3125" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Teacher Leisure Plan</t>
         </is>
       </c>
-      <c r="B1" s="36" t="n"/>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="36" t="n"/>
-      <c r="E1" s="36" t="n"/>
-      <c r="F1" s="36" t="n"/>
-      <c r="G1" s="36" t="n"/>
-      <c r="H1" s="36" t="n"/>
-      <c r="I1" s="36" t="n"/>
-      <c r="J1" s="36" t="n"/>
-      <c r="K1" s="37" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Teacher Name</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
-        <is>
-          <t>Leisure Fitmenet</t>
-        </is>
-      </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Leisure Fitment</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Period 1</t>
         </is>
       </c>
-      <c r="D2" s="29" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Period 2</t>
         </is>
       </c>
-      <c r="E2" s="29" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Period 3</t>
         </is>
       </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Period 4</t>
         </is>
       </c>
-      <c r="G2" s="29" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Period 5</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Period 6</t>
         </is>
       </c>
-      <c r="J2" s="29" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Period 7</t>
         </is>
       </c>
-      <c r="K2" s="29" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Study Hour</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>SITHA</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>BHAVANI</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>NAGAMANI</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="35" t="n"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>SAI LAKSHMI</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="35" t="n"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>MAHA</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C7" s="30" t="n"/>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H7" s="30" t="n"/>
-      <c r="I7" s="30" t="n"/>
-      <c r="J7" s="30" t="n"/>
-      <c r="K7" s="30" t="n"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TULASI</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="30" t="n"/>
-      <c r="F8" s="30" t="n"/>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H8" s="30" t="n"/>
-      <c r="I8" s="30" t="n"/>
-      <c r="J8" s="30" t="n"/>
-      <c r="K8" s="30" t="n"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>SWATHI</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="30" t="n"/>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="30" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H9" s="30" t="n"/>
-      <c r="I9" s="30" t="n"/>
-      <c r="J9" s="30" t="n"/>
-      <c r="K9" s="30" t="n"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C10" s="30" t="n"/>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="35" t="n"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>PALLAVI</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="32" t="n"/>
-      <c r="K12" s="30" t="n"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>SONU</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="F13" s="33" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="30" t="n"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>RIYA</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="32" t="n"/>
-      <c r="K14" s="33" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>SUNITHA</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="33" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>CHALAPATHI</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="G16" s="30" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H16" s="32" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="30" t="n"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>RAVI</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="30" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="30" t="n"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>D.V.RAO</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H18" s="32" t="n"/>
-      <c r="I18" s="32" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="30" t="n"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>GOWTHAM</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="G19" s="30" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H19" s="33" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="I19" s="33" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="J19" s="33" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="K19" s="33" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>BHEEMA</t>
         </is>
       </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="G20" s="30" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H20" s="33" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="I20" s="33" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="J20" s="33" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="K20" s="33" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="30" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="30" t="n"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>BEST</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="n"/>
-      <c r="G22" s="30" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H22" s="32" t="n"/>
-      <c r="I22" s="32" t="n"/>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="30" t="n"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3378,99 +2879,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
-        <is>
-          <t>Activity Plan</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Activity Plan  (each row = one combined session group)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Allowed Periods</t>
         </is>
       </c>
-      <c r="C2" s="40" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>L.K.G</t>
         </is>
       </c>
-      <c r="D2" s="40" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>U.K.G</t>
         </is>
       </c>
-      <c r="E2" s="40" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Class 1</t>
         </is>
       </c>
-      <c r="F2" s="40" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Class 2</t>
         </is>
       </c>
-      <c r="G2" s="40" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Class 3</t>
         </is>
       </c>
-      <c r="H2" s="40" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Class 4</t>
         </is>
       </c>
-      <c r="I2" s="40" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Class 5</t>
         </is>
       </c>
-      <c r="J2" s="40" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Class 6</t>
         </is>
       </c>
-      <c r="K2" s="40" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Class 7</t>
         </is>
       </c>
-      <c r="L2" s="40" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Class 8</t>
         </is>
       </c>
-      <c r="M2" s="40" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Class 9</t>
         </is>
       </c>
-      <c r="N2" s="40" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Class 10</t>
         </is>
@@ -3489,72 +2974,56 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Karate</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>P.E.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -3562,11 +3031,51 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Karate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NRCS/Requirements/NRCS_information.xlsx
+++ b/NRCS/Requirements/NRCS_information.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A4D69"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,8 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1343,7 +1361,6 @@
           <t>Hindi</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SWATHI</t>
@@ -1473,13 +1490,6 @@
           <t>Eng Gram</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>RAVI</t>
@@ -1614,11 +1624,6 @@
           <t>LALITHA</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1626,13 +1631,6 @@
           <t>Phy/Che</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>LALITHA</t>
@@ -1665,15 +1663,6 @@
           <t>Chemisty</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>BHEEMA</t>
@@ -1696,13 +1685,6 @@
           <t>Biology</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>LALITHA</t>
@@ -1735,10 +1717,6 @@
           <t>Social</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>PALLAVI</t>
@@ -1786,8 +1764,6 @@
           <t>G.K</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>NAGAMANI</t>
@@ -1828,8 +1804,6 @@
           <t>FATHIMA</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1837,8 +1811,6 @@
           <t>Computer</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>MAHESWARI</t>
@@ -1879,8 +1851,6 @@
           <t>SANGEETHA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1888,8 +1858,6 @@
           <t>P.E.T</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>P.E</t>
@@ -1947,8 +1915,6 @@
           <t>Karate</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>MARTIAL ARTS</t>
@@ -1989,8 +1955,6 @@
           <t>MARTIAL ARTS</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2141,7 +2105,6 @@
           <t>D.V.Rao</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2179,7 +2142,6 @@
           <t>Tulasi</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sangeetha</t>
@@ -2200,7 +2162,6 @@
           <t>D.V.Rao</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2291,19 +2252,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2316,19 +2269,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2341,19 +2286,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2366,19 +2303,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2391,19 +2320,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2416,19 +2337,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2441,19 +2354,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2466,19 +2371,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2491,19 +2388,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2516,19 +2405,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2566,10 +2447,6 @@
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2582,22 +2459,16 @@
           <t>MUST</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Leisure</t>
@@ -2615,22 +2486,16 @@
           <t>MUST</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Leisure</t>
@@ -2673,10 +2538,6 @@
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2689,19 +2550,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2714,19 +2567,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2739,9 +2584,6 @@
           <t>MUST</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Leisure</t>
@@ -2784,9 +2626,6 @@
           <t>MUST</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Leisure</t>
@@ -2829,19 +2668,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2854,19 +2685,11 @@
           <t>BEST</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Lunch Break</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2879,83 +2702,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Activity Plan  (each row = one combined session group)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Activity Plan  (each row = one combined session group; tick the classes that attend together)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Allowed Days</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Allowed Periods</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>L.K.G</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>U.K.G</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Class 1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Class 2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Class 3</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Class 4</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Class 5</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Class 6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Class 7</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Class 8</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Class 9</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Class 10</t>
         </is>
@@ -2967,51 +2812,52 @@
           <t>P.E.T</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>6,7</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3019,39 +2865,40 @@
           <t>P.E.T</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>6,7</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3076,6 +2923,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
